--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128877545</v>
       </c>
       <c r="B3" t="n">
-        <v>96907</v>
+        <v>96914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128877545</v>
+        <v>128934513</v>
       </c>
       <c r="B3" t="n">
         <v>96914</v>
@@ -800,29 +800,20 @@
           <t>(Mart.) Dumort</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnvikekudden, Björnvikekudden, Ög</t>
+          <t>Norr om Bjrönvikeudden, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552612</v>
+        <v>552568</v>
       </c>
       <c r="R3" t="n">
-        <v>6517692</v>
+        <v>6517695</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,15 +857,1003 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128934508</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norr om Bjrönvikeudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552566</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6517729</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128934509</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norr om Bjrönvikeudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552564</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6517706</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128934511</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr om Bjrönvikeudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552581</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6517708</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128877667</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnvikekudden, Björnvikekudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552647</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6517655</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Jens Johannesson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Jens Johannesson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128934500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96121</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norr om Bjrönvikeudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552630</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6517665</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128934502</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norr om Bjrönvikeudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>552576</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6517725</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128934507</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norr om Bjrönvikeudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552550</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6517735</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128934501</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norr om Bjrönvikeudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552577</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6517725</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128934506</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norr om Bjrönvikeudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>552524</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6517750</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128877545</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96914</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björnvikekudden, Björnvikekudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552612</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6517692</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,17 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934509</v>
+        <v>128934511</v>
       </c>
       <c r="B5" t="n">
-        <v>96914</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552564</v>
+        <v>552581</v>
       </c>
       <c r="R5" t="n">
-        <v>6517706</v>
+        <v>6517708</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934511</v>
+        <v>128934509</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>96918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552581</v>
+        <v>552564</v>
       </c>
       <c r="R6" t="n">
-        <v>6517708</v>
+        <v>6517706</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96121</v>
+        <v>96125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B9" t="n">
-        <v>96914</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R9" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1453,17 +1453,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>96918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R10" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,17 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934511</v>
+        <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>96918</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552581</v>
+        <v>552564</v>
       </c>
       <c r="R5" t="n">
-        <v>6517708</v>
+        <v>6517706</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934509</v>
+        <v>128934511</v>
       </c>
       <c r="B6" t="n">
-        <v>96918</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552564</v>
+        <v>552581</v>
       </c>
       <c r="R6" t="n">
-        <v>6517706</v>
+        <v>6517708</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>96918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R9" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1453,17 +1453,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B10" t="n">
-        <v>96918</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R10" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96125</v>
+        <v>96132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934509</v>
+        <v>128934511</v>
       </c>
       <c r="B5" t="n">
-        <v>96933</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552564</v>
+        <v>552581</v>
       </c>
       <c r="R5" t="n">
-        <v>6517706</v>
+        <v>6517708</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934511</v>
+        <v>128934509</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>96938</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552581</v>
+        <v>552564</v>
       </c>
       <c r="R6" t="n">
-        <v>6517708</v>
+        <v>6517706</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96140</v>
+        <v>96145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128934502</v>
       </c>
       <c r="B10" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934511</v>
+        <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>96941</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552581</v>
+        <v>552564</v>
       </c>
       <c r="R5" t="n">
-        <v>6517708</v>
+        <v>6517706</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934509</v>
+        <v>128934511</v>
       </c>
       <c r="B6" t="n">
-        <v>96938</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552564</v>
+        <v>552581</v>
       </c>
       <c r="R6" t="n">
-        <v>6517706</v>
+        <v>6517708</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96145</v>
+        <v>96148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>96941</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R9" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B10" t="n">
-        <v>96938</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R10" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B9" t="n">
-        <v>96941</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R9" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>96941</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R10" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>96941</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R9" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B10" t="n">
-        <v>96941</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R10" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B9" t="n">
-        <v>96951</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R9" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>96951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R10" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934509</v>
+        <v>128934511</v>
       </c>
       <c r="B5" t="n">
-        <v>96951</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552564</v>
+        <v>552581</v>
       </c>
       <c r="R5" t="n">
-        <v>6517706</v>
+        <v>6517708</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934511</v>
+        <v>128934509</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>96958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552581</v>
+        <v>552564</v>
       </c>
       <c r="R6" t="n">
-        <v>6517708</v>
+        <v>6517706</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96158</v>
+        <v>96165</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>96958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R9" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B10" t="n">
-        <v>96951</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R10" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934511</v>
+        <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>96960</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552581</v>
+        <v>552564</v>
       </c>
       <c r="R5" t="n">
-        <v>6517708</v>
+        <v>6517706</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934509</v>
+        <v>128934511</v>
       </c>
       <c r="B6" t="n">
-        <v>96958</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552564</v>
+        <v>552581</v>
       </c>
       <c r="R6" t="n">
-        <v>6517706</v>
+        <v>6517708</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96165</v>
+        <v>96167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934509</v>
+        <v>128934511</v>
       </c>
       <c r="B5" t="n">
-        <v>96960</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552564</v>
+        <v>552581</v>
       </c>
       <c r="R5" t="n">
-        <v>6517706</v>
+        <v>6517708</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934511</v>
+        <v>128934509</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>96960</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552581</v>
+        <v>552564</v>
       </c>
       <c r="R6" t="n">
-        <v>6517708</v>
+        <v>6517706</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B9" t="n">
-        <v>96960</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R9" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>96960</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R10" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934511</v>
+        <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>96960</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552581</v>
+        <v>552564</v>
       </c>
       <c r="R5" t="n">
-        <v>6517708</v>
+        <v>6517706</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934509</v>
+        <v>128934511</v>
       </c>
       <c r="B6" t="n">
-        <v>96960</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552564</v>
+        <v>552581</v>
       </c>
       <c r="R6" t="n">
-        <v>6517706</v>
+        <v>6517708</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>96986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R9" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B10" t="n">
-        <v>96960</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R10" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128877593</v>
       </c>
       <c r="B2" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B9" t="n">
-        <v>96988</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R9" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>96992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R10" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>96992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R9" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B10" t="n">
-        <v>96992</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R10" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934509</v>
+        <v>128934511</v>
       </c>
       <c r="B5" t="n">
-        <v>96992</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552564</v>
+        <v>552581</v>
       </c>
       <c r="R5" t="n">
-        <v>6517706</v>
+        <v>6517708</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934511</v>
+        <v>128934509</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>96994</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552581</v>
+        <v>552564</v>
       </c>
       <c r="R6" t="n">
-        <v>6517708</v>
+        <v>6517706</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B9" t="n">
-        <v>96992</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R9" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>96994</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R10" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934511</v>
+        <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>96998</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552581</v>
+        <v>552564</v>
       </c>
       <c r="R5" t="n">
-        <v>6517708</v>
+        <v>6517706</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934509</v>
+        <v>128934511</v>
       </c>
       <c r="B6" t="n">
-        <v>96994</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552564</v>
+        <v>552581</v>
       </c>
       <c r="R6" t="n">
-        <v>6517706</v>
+        <v>6517708</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934507</v>
+        <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>96998</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552550</v>
+        <v>552576</v>
       </c>
       <c r="R9" t="n">
-        <v>6517735</v>
+        <v>6517725</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934502</v>
+        <v>128934507</v>
       </c>
       <c r="B10" t="n">
-        <v>96994</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552576</v>
+        <v>552550</v>
       </c>
       <c r="R10" t="n">
-        <v>6517725</v>
+        <v>6517735</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128934513</v>
       </c>
       <c r="B3" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128934508</v>
       </c>
       <c r="B4" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128934509</v>
       </c>
       <c r="B5" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128877667</v>
       </c>
       <c r="B7" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128934500</v>
       </c>
       <c r="B8" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128934502</v>
       </c>
       <c r="B9" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128934501</v>
       </c>
       <c r="B11" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128877545</v>
       </c>
       <c r="B13" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -1092,6 +1092,15 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norr om Bjrönvikeudden, Ög</t>
@@ -1142,6 +1151,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1489,6 +1499,15 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norr om Bjrönvikeudden, Ög</t>
@@ -1539,6 +1558,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1683,6 +1703,15 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norr om Bjrönvikeudden, Ög</t>
@@ -1733,6 +1762,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jens Johannesson, Marika Sjödin</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>128934511</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128934507</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128934506</v>
       </c>
       <c r="B12" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128877593</v>
+        <v>128934500</v>
       </c>
       <c r="B2" t="n">
-        <v>96306</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnvikekudden, Björnvikekudden, Ög</t>
+          <t>Norr om Bjrönvikeudden, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552618</v>
+        <v>552630</v>
       </c>
       <c r="R2" t="n">
-        <v>6517699</v>
+        <v>6517665</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128934513</v>
+        <v>128877593</v>
       </c>
       <c r="B3" t="n">
-        <v>97006</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Bjrönvikeudden, Ög</t>
+          <t>Björnvikekudden, Björnvikekudden, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552568</v>
+        <v>552618</v>
       </c>
       <c r="R3" t="n">
-        <v>6517695</v>
+        <v>6517699</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128934508</v>
+        <v>128877545</v>
       </c>
       <c r="B4" t="n">
-        <v>97006</v>
+        <v>97394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,20 +897,29 @@
           <t>(Mart.) Dumort</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Bjrönvikeudden, Ög</t>
+          <t>Björnvikekudden, Björnvikekudden, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552566</v>
+        <v>552612</v>
       </c>
       <c r="R4" t="n">
-        <v>6517729</v>
+        <v>6517692</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128934509</v>
+        <v>128877667</v>
       </c>
       <c r="B5" t="n">
-        <v>97006</v>
+        <v>97394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,20 +1003,29 @@
           <t>(Mart.) Dumort</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Bjrönvikeudden, Ög</t>
+          <t>Björnvikekudden, Björnvikekudden, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552564</v>
+        <v>552647</v>
       </c>
       <c r="R5" t="n">
-        <v>6517706</v>
+        <v>6517655</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1069,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Jens Johannesson</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128934511</v>
+        <v>128934501</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>97394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,43 +1092,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norr om Bjrönvikeudden, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552581</v>
+        <v>552577</v>
       </c>
       <c r="R6" t="n">
-        <v>6517708</v>
+        <v>6517725</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1151,7 +1160,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1170,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128877667</v>
+        <v>128934502</v>
       </c>
       <c r="B7" t="n">
-        <v>97006</v>
+        <v>97394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1198,29 +1206,20 @@
           <t>(Mart.) Dumort</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnvikekudden, Björnvikekudden, Ög</t>
+          <t>Norr om Bjrönvikeudden, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552647</v>
+        <v>552576</v>
       </c>
       <c r="R7" t="n">
-        <v>6517655</v>
+        <v>6517725</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1264,22 +1263,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128934500</v>
+        <v>128934508</v>
       </c>
       <c r="B8" t="n">
-        <v>96213</v>
+        <v>97394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,21 +1286,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552630</v>
+        <v>552566</v>
       </c>
       <c r="R8" t="n">
-        <v>6517665</v>
+        <v>6517729</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128934502</v>
+        <v>128934509</v>
       </c>
       <c r="B9" t="n">
-        <v>97006</v>
+        <v>97394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552576</v>
+        <v>552564</v>
       </c>
       <c r="R9" t="n">
-        <v>6517725</v>
+        <v>6517706</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128934507</v>
+        <v>128934513</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>97394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,43 +1480,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norr om Bjrönvikeudden, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552550</v>
+        <v>552568</v>
       </c>
       <c r="R10" t="n">
-        <v>6517735</v>
+        <v>6517695</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,7 +1548,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1577,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128934501</v>
+        <v>128934503</v>
       </c>
       <c r="B11" t="n">
-        <v>97006</v>
+        <v>96458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>2818</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1612,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552577</v>
+        <v>552563</v>
       </c>
       <c r="R11" t="n">
-        <v>6517725</v>
+        <v>6517749</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1674,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128934506</v>
+        <v>128934507</v>
       </c>
       <c r="B12" t="n">
-        <v>8440</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1685,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1718,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552524</v>
+        <v>552550</v>
       </c>
       <c r="R12" t="n">
-        <v>6517750</v>
+        <v>6517735</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1781,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128877545</v>
+        <v>128934511</v>
       </c>
       <c r="B13" t="n">
-        <v>97006</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,46 +1781,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnvikekudden, Björnvikekudden, Ög</t>
+          <t>Norr om Bjrönvikeudden, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552612</v>
+        <v>552581</v>
       </c>
       <c r="R13" t="n">
-        <v>6517692</v>
+        <v>6517708</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1869,21 +1858,129 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin, Jens Johannesson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128934506</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norr om Bjrönvikeudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>552524</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6517750</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41091-2025 artfynd.xlsx
+++ b/artfynd/A 41091-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877593</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877545</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877667</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934501</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934502</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934508</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934509</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934513</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934503</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934507</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1874,6 +1934,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934511</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1981,8 +2046,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934506</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>